--- a/docs/02_基本設計/04_API・外部IF/KF-BD-009_外部インターフェース設計書.xlsx
+++ b/docs/02_基本設計/04_API・外部IF/KF-BD-009_外部インターフェース設計書.xlsx
@@ -74,7 +74,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -96,11 +96,50 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,6 +160,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -498,6 +541,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -506,6 +552,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -517,7 +565,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -530,7 +578,7 @@
           <t>KF-BD-009</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -540,10 +588,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -556,7 +604,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -569,8 +617,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -617,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -676,6 +726,52 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>実装との照合。実装状況列を追加（IF-001 は RPT-001 のみ実装済・IF-002〜004 は未実装）。IF-002 に祝日の初期データ投入（Flyway V2）を追記、IF-005（ヘルスチェック）を追加</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>IF-002 に 2028 年の祝日の初期投入（Flyway V3）を追記。他の IF に変更なし（休憩・離席は外部連携なし）</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -689,7 +785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -700,54 +796,61 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>本システムは外部システムと直接のAPI連携を行わない（MVP）。</t>
-        </is>
-      </c>
-    </row>
+          <t>本システムは外部システムと直接のAPI連携を行わない（MVP）。実装状況は 2026/10/05 時点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>IF-ID</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>IF名</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>連携先</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>方式・形式</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>実行契機</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>備考</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>実装状況</t>
         </is>
       </c>
     </row>
@@ -789,7 +892,12 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>帳票 RPT-001, RPT-002</t>
+          <t>帳票 RPT-001（API-018 format=csv）。RPT-002 は未実装</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>実装済（RPT-001）</t>
         </is>
       </c>
     </row>
@@ -831,7 +939,12 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>MVPでは SCR-304 で手動登録</t>
+          <t>MVPでは SCR-304 で手動登録。2026〜2027 年は Flyway（V2__seed_holidays.sql）、2028 年は V3__seed_holidays_2028.sql で初期投入（2028 年は推算値で内閣府の公表値との照合は未実施。次の追加は V6 以降または SCR-304）</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>未実装（CSV 取込）</t>
         </is>
       </c>
     </row>
@@ -876,6 +989,11 @@
           <t>MVPは画面内通知のみ</t>
         </is>
       </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>未実装</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -916,6 +1034,58 @@
       <c r="H7" s="8" t="inlineStr">
         <is>
           <t>仕様は連携先確定後に定義</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>未実装</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>IF-005</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ヘルスチェック</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>監視・コンテナ基盤</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>出力</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>HTTP / JSON（GET /actuator/health）</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>随時（監視側のポーリング）</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>認証不要。health のみ公開（Spring Boot Actuator）</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>実装済</t>
         </is>
       </c>
     </row>
